--- a/04-ai-governance-and-technical-lifecycle/artifacts/A-18_AI_Model_Registry.xlsx
+++ b/04-ai-governance-and-technical-lifecycle/artifacts/A-18_AI_Model_Registry.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rityshree\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Career\Portfolio\Project4\Artifacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F136E8D0-54D9-4895-829E-47CDEE56BFC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C895A528-FD9D-446C-8031-C068BD68412C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -161,9 +161,6 @@
     <t>v2.4</t>
   </si>
   <si>
-    <t>In production</t>
-  </si>
-  <si>
     <t>Concept drift &gt; 3 AUC points, or population change</t>
   </si>
   <si>
@@ -599,9 +596,6 @@
     <t>APPROVED</t>
   </si>
   <si>
-    <t>In production; independent MRM validation completed at Gate 4. Next review on retrain.</t>
-  </si>
-  <si>
     <t>Generation Model (Bedrock Claude)</t>
   </si>
   <si>
@@ -854,9 +848,6 @@
     <t>Total Components Registered</t>
   </si>
   <si>
-    <t>Components in Production</t>
-  </si>
-  <si>
     <t>Tier 1 High-Risk Core Models</t>
   </si>
   <si>
@@ -990,6 +981,15 @@
   </si>
   <si>
     <t>Change Summary</t>
+  </si>
+  <si>
+    <t>In scenario production</t>
+  </si>
+  <si>
+    <t>In Scenario Production</t>
+  </si>
+  <si>
+    <t>In scenario production; independent MRM validation completed at Gate 4. Next review on retrain.</t>
   </si>
 </sst>
 </file>
@@ -1604,7 +1604,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1627,7 +1627,7 @@
         <v>15</v>
       </c>
       <c r="G4" s="30" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1700,7 +1700,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="31" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1755,126 +1755,126 @@
         <v>20</v>
       </c>
       <c r="H5" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>47</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>26</v>
       </c>
       <c r="H6" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>48</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>53</v>
-      </c>
       <c r="E7" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>47</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>18</v>
       </c>
       <c r="H7" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" s="5" t="s">
+      <c r="G8" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="H8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="C9" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="D9" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="F9" s="7" t="s">
         <v>67</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>68</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H9" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>69</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1894,12 +1894,12 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="31" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1907,135 +1907,135 @@
         <v>2</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>99</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -2059,43 +2059,43 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="31" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="C4" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="D4" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="E4" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="F4" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="G4" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="G4" s="30" t="s">
+      <c r="H4" s="30" t="s">
         <v>112</v>
-      </c>
-      <c r="H4" s="30" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B5" s="8">
         <v>0.25</v>
@@ -2110,18 +2110,18 @@
         <v>5</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B6" s="8">
         <v>0.2</v>
@@ -2136,18 +2136,18 @@
         <v>3</v>
       </c>
       <c r="F6" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B7" s="8">
         <v>0.15</v>
@@ -2162,18 +2162,18 @@
         <v>5</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G7" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B8" s="8">
         <v>0.15</v>
@@ -2188,18 +2188,18 @@
         <v>4</v>
       </c>
       <c r="F8" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>125</v>
-      </c>
       <c r="H8" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B9" s="8">
         <v>0.1</v>
@@ -2214,18 +2214,18 @@
         <v>3</v>
       </c>
       <c r="F9" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>128</v>
-      </c>
       <c r="H9" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B10" s="8">
         <v>0.1</v>
@@ -2240,18 +2240,18 @@
         <v>3</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B11" s="8">
         <v>0.05</v>
@@ -2266,18 +2266,18 @@
         <v>4</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C12" s="10">
         <f>SUMPRODUCT($B$5:$B$11,C5:C11)</f>
@@ -2294,15 +2294,15 @@
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2325,191 +2325,191 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="31" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B4" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" s="30" t="s">
         <v>137</v>
-      </c>
-      <c r="C4" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>138</v>
       </c>
       <c r="E4" s="30" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>142</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>145</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="D7" s="7" t="s">
+      <c r="E7" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>148</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>151</v>
-      </c>
       <c r="E8" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>154</v>
-      </c>
       <c r="E10" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>155</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>160</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -2536,12 +2536,12 @@
   <sheetData>
     <row r="1" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
@@ -2549,37 +2549,37 @@
         <v>27</v>
       </c>
       <c r="B4" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="D4" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="E4" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="F4" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="G4" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="H4" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="I4" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="I4" s="20" t="s">
+      <c r="J4" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="J4" s="20" t="s">
+      <c r="K4" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="K4" s="20" t="s">
+      <c r="L4" s="20" t="s">
         <v>174</v>
-      </c>
-      <c r="L4" s="20" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="24" x14ac:dyDescent="0.3">
@@ -2587,189 +2587,189 @@
         <v>34</v>
       </c>
       <c r="B5" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="C5" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="D5" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="E5" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="F5" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="G5" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="H5" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="I5" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="I5" s="17" t="s">
+      <c r="J5" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="K5" s="21" t="s">
         <v>184</v>
       </c>
-      <c r="K5" s="21" t="s">
-        <v>185</v>
-      </c>
       <c r="L5" s="17" t="s">
-        <v>186</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B6" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="D6" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="E6" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="F6" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="G6" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="H6" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="I6" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="J6" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="I6" s="17" t="s">
+      <c r="K6" s="22" t="s">
         <v>194</v>
       </c>
-      <c r="J6" s="16" t="s">
+      <c r="L6" s="17" t="s">
         <v>195</v>
-      </c>
-      <c r="K6" s="22" t="s">
-        <v>196</v>
-      </c>
-      <c r="L6" s="17" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B7" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="F7" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="C7" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>178</v>
-      </c>
-      <c r="E7" s="17" t="s">
+      <c r="G7" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="H7" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="I7" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="J7" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="I7" s="17" t="s">
+      <c r="K7" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="L7" s="17" t="s">
         <v>203</v>
-      </c>
-      <c r="J7" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="K7" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="L7" s="17" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B8" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="D8" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="E8" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="F8" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="G8" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="H8" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="I8" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="J8" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="I8" s="17" t="s">
+      <c r="K8" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="L8" s="17" t="s">
         <v>213</v>
-      </c>
-      <c r="J8" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="K8" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="L8" s="17" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B9" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="F9" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="C9" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="D9" s="17" t="s">
+      <c r="G9" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="H9" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="E9" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="F9" s="17" t="s">
+      <c r="I9" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="G9" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="H9" s="17" t="s">
+      <c r="J9" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="I9" s="17" t="s">
+      <c r="K9" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="J9" s="16" t="s">
+      <c r="L9" s="17" t="s">
         <v>221</v>
-      </c>
-      <c r="K9" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="L9" s="17" t="s">
-        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -2795,244 +2795,244 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="20" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D4" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="F4" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="G4" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="H4" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="I4" s="20" t="s">
         <v>230</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="I4" s="20" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="24" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>34</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F5" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="24" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="D6" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="B6" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="17" t="s">
+      <c r="E6" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="G6" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="E6" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" s="16" t="s">
+      <c r="H6" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="I6" s="17" t="s">
         <v>242</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="I6" s="17" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="24" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="D7" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="B7" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>247</v>
-      </c>
       <c r="E7" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>26</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="24" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>34</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E8" s="16" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I8" s="17" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="24" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>34</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F9" s="16" t="s">
         <v>39</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="I9" s="17" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="24" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="D10" s="25" t="s">
         <v>257</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="17" t="s">
+      <c r="E10" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="16" t="s">
         <v>258</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>259</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>260</v>
       </c>
       <c r="G10" s="17" t="s">
         <v>26</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="I10" s="17" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="24" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="F11" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="B11" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>239</v>
-      </c>
-      <c r="D11" s="26" t="s">
+      <c r="G11" s="17" t="s">
         <v>263</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="H11" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="I11" s="17" t="s">
         <v>264</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>265</v>
-      </c>
-      <c r="H11" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="I11" s="17" t="s">
-        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -3056,28 +3056,28 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="27" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="37.799999999999997" x14ac:dyDescent="0.3">
       <c r="A5" s="28" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B5" s="15">
         <v>5</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>271</v>
+        <v>315</v>
       </c>
       <c r="E5" s="15">
         <v>3</v>
@@ -3085,13 +3085,13 @@
     </row>
     <row r="6" spans="1:8" ht="37.799999999999997" x14ac:dyDescent="0.3">
       <c r="A6" s="28" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B6" s="15">
         <v>1</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E6" s="22">
         <v>2</v>
@@ -3099,13 +3099,13 @@
     </row>
     <row r="7" spans="1:8" ht="37.799999999999997" x14ac:dyDescent="0.3">
       <c r="A7" s="28" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B7" s="15">
         <v>3</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E7" s="23">
         <v>3</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="8" spans="1:8" ht="37.799999999999997" x14ac:dyDescent="0.3">
       <c r="A8" s="28" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B8" s="15">
         <v>1</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E8" s="15">
         <v>1</v>
@@ -3127,30 +3127,30 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="D13" s="20" t="s">
         <v>279</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>282</v>
       </c>
       <c r="E13" s="20" t="s">
         <v>32</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H13" s="20" t="s">
         <v>15</v>
@@ -3158,106 +3158,106 @@
     </row>
     <row r="14" spans="1:8" ht="36" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>283</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="D14" s="17" t="s">
         <v>285</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="E14" s="17" t="s">
         <v>286</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="F14" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="G14" s="23" t="s">
         <v>288</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="H14" s="22" t="s">
         <v>289</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>290</v>
-      </c>
-      <c r="G14" s="23" t="s">
-        <v>291</v>
-      </c>
-      <c r="H14" s="22" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="36" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>291</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="D15" s="17" t="s">
         <v>293</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>294</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>295</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>296</v>
       </c>
       <c r="E15" s="17" t="s">
         <v>26</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H15" s="29" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="D16" s="17" t="s">
         <v>300</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="E16" s="17" t="s">
         <v>301</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="F16" s="16" t="s">
         <v>302</v>
       </c>
-      <c r="D16" s="17" t="s">
-        <v>303</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>304</v>
-      </c>
-      <c r="F16" s="16" t="s">
-        <v>305</v>
-      </c>
       <c r="G16" s="23" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="24" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="D17" s="17" t="s">
         <v>306</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>307</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>308</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>309</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H17" s="29" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
